--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -882,6 +882,171 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06 20:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,51 +900,63 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>117120</v>
+      </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+        <v>412</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>242</v>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6976</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -966,51 +978,63 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>29888</v>
+      </c>
       <c r="F14" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="n">
+        <v>520</v>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-06 20:32</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>65820</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>
@@ -1032,18 +1056,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>21987</v>
+      </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+        <v>145</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>58</v>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06 20:32</t>
+          <t>2026-07-07 12:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29888</v>
+        <v>65820</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>313</v>
+        <v>125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>520</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1021,57 +1021,18 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>65820</v>
+        <v>21987</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-07 12:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>21987</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2026-07-07 12:57</t>
         </is>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1038,6 +1038,45 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>29910</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>542</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 19:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,24 +900,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>117120</v>
+        <v>117130</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>412</v>
+        <v>493</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -939,24 +939,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>6976</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>-14</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -978,24 +978,18 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>65820</v>
-      </c>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1001,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1017,24 +1011,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21987</v>
+        <v>65832</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:57</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1040,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1056,24 +1050,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29910</v>
+        <v>22010</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>378</v>
+        <v>176</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>542</v>
+        <v>81</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07 19:26</t>
+          <t>2026-07-08 16:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,24 +900,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>117130</v>
+        <v>117163</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>493</v>
+        <v>585</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -939,24 +939,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6976</v>
+        <v>6977</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -989,7 +989,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1011,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>65832</v>
+        <v>65851</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>
@@ -1050,24 +1050,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22010</v>
+        <v>22014</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08 16:20</t>
+          <t>2026-07-09 13:42</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -882,195 +882,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Academias</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>117163</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>585</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>285</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Personal</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>6977</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>65851</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>124</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>S28/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>22014</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-09 13:42</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -882,6 +882,201 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>117168</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>585</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>6977</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>29999</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>460</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>65851</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>S28/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>22018</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 14:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,63 +900,63 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>117168</v>
+        <v>117203</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>585</v>
+        <v>681</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>6977</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6985</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -978,63 +978,63 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29999</v>
+        <v>30124</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>460</v>
+        <v>537</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>631</v>
+        <v>756</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>S28/2026</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>65851</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-09 14:52</t>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>65869</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22018</v>
+        <v>22037</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09 14:52</t>
+          <t>2026-07-10 17:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,24 +900,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>117203</v>
+        <v>117217</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>681</v>
+        <v>771</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>356</v>
+        <v>432</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -939,24 +939,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>6985</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -978,24 +978,24 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>30124</v>
+        <v>30162</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>537</v>
+        <v>664</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>65869</v>
+        <v>65865</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22037</v>
+        <v>22047</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10 17:13</t>
+          <t>2026-07-11 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -900,24 +900,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>117217</v>
+        <v>117228</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>771</v>
+        <v>848</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>432</v>
+        <v>498</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -939,24 +939,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6985</v>
+        <v>6980</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -978,24 +978,24 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>30162</v>
+        <v>30189</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>664</v>
+        <v>754</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>65865</v>
+        <v>65872</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>12/07/2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>22047</v>
+        <v>22058</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 14:40</t>
+          <t>2026-07-12 14:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1077,6 +1077,201 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>117239</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>991</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>630</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6982</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>30229</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>874</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>861</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>65865</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>321</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>S29/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>22065</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>419</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,63 +1095,63 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117239</v>
+        <v>117263</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>991</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>6982</v>
-      </c>
-      <c r="F18" s="2" t="n">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>6983</v>
+      </c>
+      <c r="F18" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="G18" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1173,63 +1173,63 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30229</v>
+        <v>30284</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>874</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>861</v>
+        <v>916</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>S29/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>65865</v>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>14/07/2026</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>65875</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>321</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13 17:40</t>
+      <c r="G20" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22065</v>
+        <v>22072</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>419</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 17:40</t>
+          <t>2026-07-14 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,24 +1095,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117263</v>
+        <v>117294</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>991</v>
+        <v>1099</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>606</v>
+        <v>683</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6983</v>
+        <v>6997</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1173,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30284</v>
+        <v>30325</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>874</v>
+        <v>946</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>916</v>
+        <v>957</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1212,24 +1212,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>65875</v>
+        <v>65877</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22072</v>
+        <v>22096</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14 15:18</t>
+          <t>2026-07-15 15:18</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,24 +1095,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117294</v>
+        <v>117317</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1099</v>
+        <v>1191</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>683</v>
+        <v>752</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>6997</v>
+        <v>7012</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1173,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30325</v>
+        <v>30380</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>946</v>
+        <v>1041</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>957</v>
+        <v>1012</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1212,24 +1212,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>65877</v>
+        <v>65879</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22096</v>
+        <v>22104</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>458</v>
+        <v>496</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 15:18</t>
+          <t>2026-07-16 15:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,24 +1095,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117317</v>
+        <v>117344</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1191</v>
+        <v>1287</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>752</v>
+        <v>821</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7012</v>
+        <v>7024</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1173,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30380</v>
+        <v>30436</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1041</v>
+        <v>1105</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1012</v>
+        <v>1068</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1212,24 +1212,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>65879</v>
+        <v>65878</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22104</v>
+        <v>22132</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>496</v>
+        <v>527</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 15:54</t>
+          <t>2026-07-17 15:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,24 +1095,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117344</v>
+        <v>117370</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1287</v>
+        <v>1381</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>821</v>
+        <v>889</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7024</v>
+        <v>7028</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1173,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30436</v>
+        <v>30471</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1105</v>
+        <v>1182</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1068</v>
+        <v>1103</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1212,24 +1212,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>65878</v>
+        <v>65889</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>18/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22132</v>
+        <v>22140</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17 15:05</t>
+          <t>2026-07-18 12:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1095,24 +1095,24 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>117370</v>
+        <v>117394</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1381</v>
+        <v>1479</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>889</v>
+        <v>963</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1134,24 +1134,24 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7028</v>
+        <v>7038</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1173,24 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>30471</v>
+        <v>30534</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1182</v>
+        <v>1255</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1103</v>
+        <v>1166</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1212,24 +1212,24 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>65889</v>
+        <v>65918</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>
@@ -1251,24 +1251,24 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22140</v>
+        <v>22150</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 12:46</t>
+          <t>2026-07-19 14:40</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1272,6 +1272,201 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>117410</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1028</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>532</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>7058</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>30574</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>65915</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>S30/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>22160</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>231</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,63 +1290,63 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117410</v>
+        <v>117428</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1560</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>7058</v>
-      </c>
-      <c r="F23" s="3" t="n">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>7068</v>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="G23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1368,63 +1368,63 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30574</v>
+        <v>30649</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>1341</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1206</v>
+        <v>1281</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>S30/2026</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>20/07/2026</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>65915</v>
-      </c>
-      <c r="F25" s="3" t="n">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>65921</v>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>489</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:13</t>
+      <c r="G25" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22160</v>
+        <v>22183</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>619</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20 16:13</t>
+          <t>2026-07-21 16:01</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,24 +1290,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117428</v>
+        <v>117459</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1560</v>
+        <v>1726</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1010</v>
+        <v>1145</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7068</v>
+        <v>7079</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1368,24 +1368,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30649</v>
+        <v>30716</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1341</v>
+        <v>1482</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1281</v>
+        <v>1348</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65921</v>
+        <v>65937</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22183</v>
+        <v>22189</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>619</v>
+        <v>669</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21 16:01</t>
+          <t>2026-07-22 15:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,24 +1290,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117459</v>
+        <v>117512</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1726</v>
+        <v>1830</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1145</v>
+        <v>1196</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7079</v>
+        <v>7087</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1368,24 +1368,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30716</v>
+        <v>30789</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1482</v>
+        <v>1587</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1348</v>
+        <v>1421</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65937</v>
+        <v>65934</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>532</v>
+        <v>567</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>322</v>
+        <v>360</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22189</v>
+        <v>22195</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>669</v>
+        <v>711</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>409</v>
+        <v>445</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22 15:57</t>
+          <t>2026-07-23 16:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,24 +1290,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117512</v>
+        <v>117536</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1830</v>
+        <v>1955</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1196</v>
+        <v>1297</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7087</v>
+        <v>7097</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1368,24 +1368,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30789</v>
+        <v>30868</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1587</v>
+        <v>1681</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1421</v>
+        <v>1500</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65934</v>
+        <v>65942</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22195</v>
+        <v>22203</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>711</v>
+        <v>749</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23 16:11</t>
+          <t>2026-07-24 15:22</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,24 +1290,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117536</v>
+        <v>117576</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1955</v>
+        <v>2061</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1297</v>
+        <v>1363</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7097</v>
+        <v>7109</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1368,24 +1368,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30868</v>
+        <v>30939</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1681</v>
+        <v>1782</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1500</v>
+        <v>1571</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65942</v>
+        <v>65953</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>594</v>
+        <v>625</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>25/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22203</v>
+        <v>22211</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>749</v>
+        <v>771</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:22</t>
+          <t>2026-07-25 14:51</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1290,24 +1290,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117576</v>
+        <v>117607</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2061</v>
+        <v>2165</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1363</v>
+        <v>1436</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1329,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7109</v>
+        <v>7116</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1368,24 +1368,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>30939</v>
+        <v>30985</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1782</v>
+        <v>1884</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1571</v>
+        <v>1617</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>65953</v>
+        <v>65962</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1446,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>22211</v>
+        <v>22214</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>489</v>
+        <v>511</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:51</t>
+          <t>2026-07-26 14:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1467,6 +1467,201 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>117620</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2254</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>1512</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>742</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>7122</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>233</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>31027</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1971</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>1659</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>65974</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>693</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>446</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>S31/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>22223</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>822</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>528</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 17:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1485,63 +1485,63 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117620</v>
+        <v>117601</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2254</v>
+        <v>2321</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1512</v>
+        <v>1598</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>7122</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="G28" s="2" t="n">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>7135</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="H28" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="H28" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1563,63 +1563,63 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31027</v>
+        <v>31096</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1971</v>
+        <v>2039</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1659</v>
+        <v>1728</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>S31/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>01/07/2026</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>27/07/2026</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>65974</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>693</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>446</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27 17:21</t>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>65994</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>718</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>451</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>27/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22223</v>
+        <v>22222</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>528</v>
+        <v>556</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 17:21</t>
+          <t>2026-07-28 16:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1485,24 +1485,24 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117601</v>
+        <v>117672</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2321</v>
+        <v>2415</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1598</v>
+        <v>1621</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>723</v>
+        <v>794</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1524,24 +1524,24 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7135</v>
+        <v>7143</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1563,24 +1563,24 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31096</v>
+        <v>31196</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2039</v>
+        <v>2121</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1728</v>
+        <v>1828</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1602,24 +1602,24 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>65994</v>
+        <v>66011</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>718</v>
+        <v>753</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22222</v>
+        <v>22255</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>849</v>
+        <v>889</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>293</v>
+        <v>326</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28 16:28</t>
+          <t>2026-07-29 16:07</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1485,24 +1485,24 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117672</v>
+        <v>117751</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2415</v>
+        <v>2531</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1621</v>
+        <v>1658</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>794</v>
+        <v>873</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1524,24 +1524,24 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7143</v>
+        <v>7151</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1563,24 +1563,24 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31196</v>
+        <v>31274</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2121</v>
+        <v>2233</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1828</v>
+        <v>1906</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1602,24 +1602,24 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
         <v>66011</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>753</v>
+        <v>789</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>469</v>
+        <v>505</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>284</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22255</v>
+        <v>22276</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>889</v>
+        <v>930</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29 16:07</t>
+          <t>2026-07-30 16:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1485,24 +1485,24 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117751</v>
+        <v>117800</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2531</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1658</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>873</v>
+        <v>922</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1524,24 +1524,24 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7151</v>
+        <v>7161</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1563,24 +1563,24 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31274</v>
+        <v>31358</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2233</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1906</v>
+        <v>1990</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1602,24 +1602,24 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>66011</v>
+        <v>66023</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22276</v>
+        <v>22294</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30 16:10</t>
+          <t>2026-07-31 16:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1480,16 +1480,16 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117800</v>
+        <v>117818</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -1498,11 +1498,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>922</v>
+        <v>211</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1519,16 +1519,16 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7161</v>
+        <v>7168</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1537,11 +1537,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>171</v>
+        <v>52</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1558,16 +1558,16 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31358</v>
+        <v>31397</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
@@ -1576,11 +1576,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1990</v>
+        <v>412</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1597,16 +1597,16 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>66023</v>
+        <v>66036</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
@@ -1615,11 +1615,11 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>296</v>
+        <v>74</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>
@@ -1636,16 +1636,16 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22294</v>
+        <v>22306</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -1654,11 +1654,11 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>365</v>
+        <v>92</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31 16:25</t>
+          <t>2026-08-01 14:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1485,11 +1485,11 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>117818</v>
+        <v>117831</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -1498,11 +1498,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1524,11 +1524,11 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>7168</v>
+        <v>7169</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0</v>
@@ -1537,11 +1537,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1563,11 +1563,11 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>31397</v>
+        <v>31426</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
@@ -1576,11 +1576,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1602,11 +1602,11 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>66036</v>
+        <v>66041</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>0</v>
@@ -1615,11 +1615,11 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>
@@ -1641,11 +1641,11 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>22306</v>
+        <v>22314</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -1654,11 +1654,11 @@
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:45</t>
+          <t>2026-08-02 11:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1662,6 +1662,201 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>117854</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7183</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>31475</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>66052</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>S32/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>22308</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 12:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,63 +1680,63 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117854</v>
+        <v>117920</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>247</v>
+        <v>313</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>7183</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>7196</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1758,63 +1758,63 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31475</v>
+        <v>31551</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>490</v>
+        <v>566</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>S32/2026</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>66052</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-03 12:50</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>04/08/2026</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>66055</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>
@@ -1836,24 +1836,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22308</v>
+        <v>22326</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03 12:50</t>
+          <t>2026-08-04 11:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,11 +1680,11 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117920</v>
+        <v>117972</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>170</v>
@@ -1693,11 +1693,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>313</v>
+        <v>365</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1719,11 +1719,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7196</v>
+        <v>7201</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>33</v>
@@ -1732,11 +1732,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1758,11 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31551</v>
+        <v>31599</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>136</v>
@@ -1771,11 +1771,11 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1797,11 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>66055</v>
+        <v>66069</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>48</v>
@@ -1810,11 +1810,11 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22326</v>
+        <v>22339</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>55</v>
@@ -1849,11 +1849,11 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04 11:59</t>
+          <t>2026-08-05 11:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,11 +1680,11 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117972</v>
+        <v>118003</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>170</v>
@@ -1693,11 +1693,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1719,11 +1719,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7201</v>
+        <v>7210</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>33</v>
@@ -1732,11 +1732,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1758,11 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31599</v>
+        <v>31639</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>136</v>
@@ -1771,11 +1771,11 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>614</v>
+        <v>654</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1797,11 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>66069</v>
+        <v>66072</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>48</v>
@@ -1810,11 +1810,11 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22339</v>
+        <v>22353</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>55</v>
@@ -1849,11 +1849,11 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05 11:53</t>
+          <t>2026-08-06 11:58</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,11 +1680,11 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118003</v>
+        <v>118055</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>170</v>
@@ -1693,11 +1693,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>396</v>
+        <v>448</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1719,11 +1719,11 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7210</v>
+        <v>7214</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>33</v>
@@ -1732,11 +1732,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1758,11 +1758,11 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31639</v>
+        <v>31682</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>136</v>
@@ -1771,11 +1771,11 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>654</v>
+        <v>697</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1797,11 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>66072</v>
+        <v>66079</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>48</v>
@@ -1810,11 +1810,11 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22353</v>
+        <v>22366</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>55</v>
@@ -1849,11 +1849,11 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06 11:58</t>
+          <t>2026-08-07 10:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,24 +1680,24 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118055</v>
+        <v>118082</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>170</v>
+        <v>533</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1719,24 +1719,24 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7214</v>
+        <v>7226</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1758,24 +1758,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31682</v>
+        <v>31726</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>136</v>
+        <v>391</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>697</v>
+        <v>741</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1797,24 +1797,24 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>66079</v>
+        <v>66080</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>48</v>
+        <v>134</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>
@@ -1836,24 +1836,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>08/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22366</v>
+        <v>22376</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07 10:44</t>
+          <t>2026-08-08 10:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1680,24 +1680,24 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118082</v>
+        <v>118113</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>533</v>
+        <v>713</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>58</v>
+        <v>207</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>475</v>
+        <v>506</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1719,24 +1719,24 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7226</v>
+        <v>7235</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1758,24 +1758,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>31726</v>
+        <v>31770</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>391</v>
+        <v>532</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>741</v>
+        <v>785</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1797,24 +1797,24 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>66080</v>
+        <v>66093</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>
@@ -1836,24 +1836,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>08/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>22376</v>
+        <v>22375</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08 10:24</t>
+          <t>2026-08-09 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1857,6 +1857,201 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>118151</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>816</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>544</v>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>7243</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>31809</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>605</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>824</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>66095</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>S33/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>22383</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,63 +1875,63 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118151</v>
+        <v>118206</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>816</v>
+        <v>894</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>544</v>
+        <v>599</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>S33/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>7243</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>7250</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -1953,63 +1953,63 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>31809</v>
+        <v>31871</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>605</v>
+        <v>661</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>824</v>
+        <v>886</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>S33/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>66095</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10 11:01</t>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>66111</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22383</v>
+        <v>22397</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01</t>
+          <t>2026-08-11 10:46</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,24 +1875,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118206</v>
+        <v>118229</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>894</v>
+        <v>1030</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>295</v>
+        <v>408</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>599</v>
+        <v>622</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7250</v>
+        <v>7261</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>31871</v>
+        <v>31917</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>661</v>
+        <v>737</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1992,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>66111</v>
+        <v>66114</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22397</v>
+        <v>22409</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11 10:46</t>
+          <t>2026-08-12 10:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,24 +1875,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118229</v>
+        <v>118271</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1030</v>
+        <v>1115</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>622</v>
+        <v>664</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7261</v>
+        <v>7275</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>31917</v>
+        <v>31972</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>737</v>
+        <v>813</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>932</v>
+        <v>987</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1992,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>66114</v>
+        <v>66116</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22409</v>
+        <v>22434</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12 10:54</t>
+          <t>2026-08-13 10:53</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,24 +1875,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118271</v>
+        <v>118285</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1115</v>
+        <v>1226</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>451</v>
+        <v>548</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7275</v>
+        <v>7281</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>31972</v>
+        <v>32033</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>813</v>
+        <v>912</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>987</v>
+        <v>1048</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1992,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>66116</v>
+        <v>66113</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22434</v>
+        <v>22440</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>345</v>
+        <v>378</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 10:53</t>
+          <t>2026-08-14 10:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,24 +1875,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118285</v>
+        <v>118323</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1226</v>
+        <v>1318</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>548</v>
+        <v>602</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1914,14 +1914,14 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
         <v>7281</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>32033</v>
+        <v>32083</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>912</v>
+        <v>1003</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1992,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>66113</v>
+        <v>66118</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>15/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22440</v>
+        <v>22451</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 10:49</t>
+          <t>2026-08-15 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -1875,24 +1875,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>118323</v>
+        <v>118331</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1318</v>
+        <v>1410</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>602</v>
+        <v>686</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>7281</v>
+        <v>7291</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1953,24 +1953,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>32083</v>
+        <v>32134</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1003</v>
+        <v>1087</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1098</v>
+        <v>1149</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -1992,24 +1992,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>66118</v>
+        <v>66123</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>
@@ -2031,24 +2031,24 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>22451</v>
+        <v>22460</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14</t>
+          <t>2026-08-16 10:15</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2052,201 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>118333</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>726</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>7303</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>32184</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1199</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>66122</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>394</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>S34/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>22459</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,63 +2070,63 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118333</v>
+        <v>118382</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1508</v>
+        <v>1608</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>782</v>
+        <v>833</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>726</v>
+        <v>775</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>7303</v>
-      </c>
-      <c r="F43" s="3" t="n">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>7313</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -2148,63 +2148,63 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32184</v>
+        <v>32222</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1155</v>
+        <v>1228</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>S34/2026</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>17/08/2026</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>66122</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>394</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17 10:23</t>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>66127</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22459</v>
+        <v>22484</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:23</t>
+          <t>2026-08-18 10:20</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,24 +2070,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118382</v>
+        <v>118436</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1608</v>
+        <v>1724</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>833</v>
+        <v>895</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>775</v>
+        <v>829</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7313</v>
+        <v>7322</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32222</v>
+        <v>32285</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1228</v>
+        <v>1297</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1237</v>
+        <v>1300</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66127</v>
+        <v>66140</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22484</v>
+        <v>22498</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:20</t>
+          <t>2026-08-19 10:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,24 +2070,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118436</v>
+        <v>118466</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1724</v>
+        <v>1840</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>895</v>
+        <v>981</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>829</v>
+        <v>859</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7322</v>
+        <v>7327</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32285</v>
+        <v>32684</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1297</v>
+        <v>1393</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1300</v>
+        <v>1699</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66140</v>
+        <v>66143</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>273</v>
+        <v>308</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22498</v>
+        <v>22515</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>529</v>
+        <v>564</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:26</t>
+          <t>2026-08-20 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,24 +2070,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118466</v>
+        <v>118513</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1840</v>
+        <v>1952</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>981</v>
+        <v>1046</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>859</v>
+        <v>906</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7327</v>
+        <v>7331</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32684</v>
+        <v>32896</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1393</v>
+        <v>1778</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1699</v>
+        <v>1911</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66143</v>
+        <v>66150</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22515</v>
+        <v>22521</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>564</v>
+        <v>600</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:21</t>
+          <t>2026-08-21 10:21</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,24 +2070,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118513</v>
+        <v>118561</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1952</v>
+        <v>2048</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1046</v>
+        <v>1094</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>906</v>
+        <v>954</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7331</v>
+        <v>7341</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>32896</v>
+        <v>33002</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1778</v>
+        <v>2058</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1911</v>
+        <v>2017</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66150</v>
+        <v>66162</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>22/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22521</v>
+        <v>22548</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:21</t>
+          <t>2026-08-22 10:14</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2070,24 +2070,24 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118561</v>
+        <v>118580</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2048</v>
+        <v>2145</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1094</v>
+        <v>1172</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>954</v>
+        <v>973</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2109,24 +2109,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>7341</v>
+        <v>7339</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2148,24 +2148,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>33002</v>
+        <v>33095</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>2058</v>
+        <v>2180</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2017</v>
+        <v>2110</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66162</v>
+        <v>66166</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>22/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>22548</v>
+        <v>22567</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:14</t>
+          <t>2026-08-23 10:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2247,201 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>118596</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2228</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>1239</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>989</v>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>7350</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>234</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>33267</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2320</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>2282</v>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>66183</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>602</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>S35/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>22581</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>701</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>334</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>367</v>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24 10:29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,63 +2265,63 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118596</v>
+        <v>118630</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2228</v>
+        <v>2325</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1239</v>
+        <v>1302</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>989</v>
+        <v>1023</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>7350</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>268</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>7360</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -2343,63 +2343,63 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33267</v>
+        <v>33370</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2320</v>
+        <v>2508</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2282</v>
+        <v>2385</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>S35/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>01/08/2026</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>66183</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>602</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>381</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>221</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24 10:29</t>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>66193</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>631</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22581</v>
+        <v>22585</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:29</t>
+          <t>2026-08-25 10:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,24 +2265,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118630</v>
+        <v>118657</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2325</v>
+        <v>2422</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1302</v>
+        <v>1372</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1023</v>
+        <v>1050</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7360</v>
+        <v>7369</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2343,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33370</v>
+        <v>33474</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2508</v>
+        <v>2646</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2385</v>
+        <v>2489</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66193</v>
+        <v>66201</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22585</v>
+        <v>22603</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:25</t>
+          <t>2026-08-26 10:28</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,24 +2265,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118657</v>
+        <v>118724</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2422</v>
+        <v>2629</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1372</v>
+        <v>1512</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1050</v>
+        <v>1117</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7369</v>
+        <v>7379</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2343,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33474</v>
+        <v>33625</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2646</v>
+        <v>2900</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2489</v>
+        <v>2640</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66201</v>
+        <v>66204</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>421</v>
+        <v>466</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22603</v>
+        <v>22614</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>750</v>
+        <v>823</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:28</t>
+          <t>2026-08-27 20:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,24 +2265,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118724</v>
+        <v>118782</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2629</v>
+        <v>2733</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1512</v>
+        <v>1558</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1117</v>
+        <v>1175</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7379</v>
+        <v>7384</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2343,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33625</v>
+        <v>33728</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2900</v>
+        <v>3042</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2640</v>
+        <v>2743</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66204</v>
+        <v>66223</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>708</v>
+        <v>743</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22614</v>
+        <v>22639</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>823</v>
+        <v>855</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:08</t>
+          <t>2026-08-28 21:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,24 +2265,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118782</v>
+        <v>118817</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>2733</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1558</v>
+        <v>1523</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1175</v>
+        <v>1210</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7384</v>
+        <v>7387</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>325</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2343,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33728</v>
+        <v>33820</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>3042</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>299</v>
+        <v>207</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2743</v>
+        <v>2835</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66223</v>
+        <v>66233</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>743</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>29/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22639</v>
+        <v>22638</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>855</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:05</t>
+          <t>2026-08-29 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2265,24 +2265,24 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>118817</v>
+        <v>118869</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>2733</v>
+        <v>2852</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1523</v>
+        <v>1590</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>1210</v>
+        <v>1262</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2304,24 +2304,24 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>7387</v>
+        <v>7391</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2343,24 +2343,24 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33820</v>
+        <v>33970</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>3042</v>
+        <v>3187</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>2835</v>
+        <v>2985</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2382,24 +2382,24 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>66233</v>
+        <v>66246</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>743</v>
+        <v>778</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>22638</v>
+        <v>22635</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>855</v>
+        <v>889</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29 14:49</t>
+          <t>2026-08-30 14:39</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2442,6 +2442,201 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>118904</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1297</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>7393</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>34149</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>3164</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>66244</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>S36/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>22635</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>421</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2455,16 +2455,16 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>118904</v>
+        <v>118949</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0</v>
@@ -2473,50 +2473,50 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1297</v>
+        <v>80</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>7393</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>7404</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2533,16 +2533,16 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34149</v>
+        <v>34303</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0</v>
@@ -2551,50 +2551,50 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>3164</v>
+        <v>333</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>S36/2026</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>66244</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>282</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:19</t>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>66271</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>
@@ -2611,16 +2611,16 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>22635</v>
+        <v>22656</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -2629,11 +2629,11 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:19</t>
+          <t>2026-09-01 14:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2460,11 +2460,11 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>118949</v>
+        <v>119026</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>0</v>
@@ -2473,11 +2473,11 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2499,11 +2499,11 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>7404</v>
+        <v>7410</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0</v>
@@ -2512,11 +2512,11 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2538,11 +2538,11 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34303</v>
+        <v>34507</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>0</v>
@@ -2551,11 +2551,11 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>333</v>
+        <v>537</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2577,11 +2577,11 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>66271</v>
+        <v>66287</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>0</v>
@@ -2590,11 +2590,11 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>
@@ -2616,11 +2616,11 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>22656</v>
+        <v>22673</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>0</v>
@@ -2629,11 +2629,11 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:23</t>
+          <t>2026-09-02 13:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2460,24 +2460,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>119026</v>
+        <v>119048</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>7410</v>
+        <v>7416</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2538,24 +2538,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34507</v>
+        <v>34599</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>537</v>
+        <v>629</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2577,24 +2577,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>66287</v>
+        <v>66295</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>
@@ -2616,24 +2616,24 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>22673</v>
+        <v>22685</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:57</t>
+          <t>2026-09-03 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2460,24 +2460,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>119048</v>
+        <v>119114</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>144</v>
+        <v>250</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>7416</v>
+        <v>7419</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2538,24 +2538,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34599</v>
+        <v>34655</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>256</v>
+        <v>375</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>629</v>
+        <v>685</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2577,24 +2577,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>66295</v>
+        <v>66292</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>
@@ -2616,24 +2616,24 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>22685</v>
+        <v>22708</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:59</t>
+          <t>2026-09-04 13:56</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2460,24 +2460,18 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>119114</v>
-      </c>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>245</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2493,18 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>7419</v>
-      </c>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2538,24 +2526,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>05/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34655</v>
+        <v>34678</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>375</v>
+        <v>478</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>685</v>
+        <v>708</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2577,24 +2565,18 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>66292</v>
-      </c>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>46</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>
@@ -2616,24 +2598,18 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>22708</v>
-      </c>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>73</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:56</t>
+          <t>2026-09-05 13:11</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E52" s="2" t="n"/>
@@ -2471,7 +2471,7 @@
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E53" s="2" t="n"/>
@@ -2504,7 +2504,7 @@
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2526,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34678</v>
+        <v>34747</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>478</v>
+        <v>535</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>708</v>
+        <v>777</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E55" s="2" t="n"/>
@@ -2576,7 +2576,7 @@
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="E56" s="2" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:11</t>
+          <t>2026-09-06 13:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2613,6 +2613,171 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n"/>
+      <c r="F59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>S37/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n"/>
+      <c r="F61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 15:27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,40 +2642,40 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,40 +2708,40 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>S37/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 15:27</t>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07 15:27</t>
+          <t>2026-09-08 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,7 +2708,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2741,7 +2741,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:00</t>
+          <t>2026-09-09 14:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,7 +2708,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2741,7 +2741,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:05</t>
+          <t>2026-09-10 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,7 +2708,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2741,7 +2741,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:59</t>
+          <t>2026-09-11 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,7 +2708,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2741,7 +2741,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00</t>
+          <t>2026-09-12 13:16</t>
         </is>
       </c>
     </row>
